--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260813.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260813.xlsx
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>12,795,000</t>
+          <t>28,657,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>28,657,000</t>
+          <t>12,795,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>8,032,000</t>
+          <t>2,960,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,960,000</t>
+          <t>8,032,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
